--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0117.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0117.xlsx
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Aaaaa! Ta hủy đăng ký được không?!</t>
+          <t>Aaaaa! Tao hủy đăng ký được không?!</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Nửa đêm. Khu vườn. Đến nếu cậu dám. Còn không… chắc cậu là loại "ngủ sớm" rồi.</t>
+          <t>Nửa đêm. Khu vườn. Đến nếu mày dám. Còn không… chắc mày là loại "ngủ sớm" rồi.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hừ! Cứ làm đi! Nếu cậu sợ không dám đối mặt với thế giới siêu nhiên, thì cứ việc!</t>
+          <t>Hừ! Cứ làm đi! Nếu mày sợ không dám đối mặt với thế giới siêu nhiên, thì cứ việc!</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Aaaaa! Ta hủy đăng ký được không?!</t>
+          <t>Aaaaa! Tao hủy đăng ký được không?!</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Đợi đã. Ai bảo ta tham gia đâu?</t>
+          <t>Đợi đã. Ai bảo tao tham gia đâu?</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Không thể nào! Cậu thật sự từ chối một cơ hội &lt;i&gt;hiếm có&lt;/i&gt; như thế này sao?!</t>
+          <t>Không thể nào! Mày thật sự từ chối một cơ hội &lt;i&gt;hiếm có&lt;/i&gt; như thế này sao?!</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Giờ người đã ở đây rồi, ta sẽ không để ngươi chạy thoát đâu. Một tài năng như ngươi? Giờ là của ta rồi!</t>
+          <t>Giờ người đã ở đây rồi, tao sẽ không để mày chạy thoát đâu. Một tài năng như mày? Giờ là của tao rồi!</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đừng lo nhé! Tuy trên giấy tờ tụi ta không "chính thức", nhưng ngân sách và quyền lợi thành viên chẳng kém gì đâu!</t>
+          <t>Đừng lo nhé! Tuy trên giấy tờ tụi tao không "chính thức", nhưng ngân sách và quyền lợi thành viên chẳng kém gì đâu!</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Vậy nên hãy mở to mắt ra nhé, {Male=anh Chuyên Gia;Female=chị Chuyên Gia}.</t>
+          <t>Vậy nên hãy mở to mắt ra nhé, {Male=Mr. Rationality;Female=Ms. Rationality}.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Ừ, xin lỗi. Chỉ là… ta vẫn thấy bực mình mỗi khi nghe ai nhắc đến Mayo thôi.</t>
+          <t>Ừ, xin lỗi. Chỉ là… tao vẫn thấy bực mình mỗi khi nghe ai nhắc đến Mayo thôi.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Nhớ lại thì, những lần tiếp xúc của chúng ta có nhiều điều kỳ lạ. Nhưng ta không nghĩ cô ấy cố tình che giấu điều gì.</t>
+          <t>Nhớ lại thì, những lần tiếp xúc của chúng ta có nhiều điều kỳ lạ. Nhưng tao không nghĩ cô ấy cố tình che giấu điều gì.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Ừm. Ta không sao. Chỉ là... không thể quay lại thôi.</t>
+          <t>Ừm. Tao không sao. Chỉ là... không thể quay lại thôi.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>...Cậu thật sự nghĩ là ta sẽ nói thế hả?!</t>
+          <t>...Cậu thật sự nghĩ là tao sẽ nói thế hả?!</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Nhưng cái đường hầm sương mù này... Ta thề là đã nghe đâu đó một truyền thuyết đô thị về nó, nhưng ở đâu nhỉ...?</t>
+          <t>Nhưng cái đường hầm sương mù này... Tao thề là đã nghe đâu đó một truyền thuyết đô thị về nó, nhưng ở đâu nhỉ...?</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Hừ. Ngươi muốn chết à, nhóc?</t>
+          <t>Hừ. Mày muốn chết à, nhóc?</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Ta nổi da gà rồi đấy… Này, cậu không phải bịa chuyện này ra để trốn làm thêm giờ đấy chứ?</t>
+          <t>Tao nổi da gà rồi đấy… Này, cậu không phải bịa chuyện này ra để trốn làm thêm giờ đấy chứ?</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Hừ. Muốn làm nhân viên gương mẫu à? Tự nhiên. Còn ta? Ta tan làm đúng giờ thôi.</t>
+          <t>Hừ. Muốn làm nhân viên gương mẫu à? Tự nhiên. Còn tao? Tao tan làm đúng giờ thôi.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nhìn lâu vào thế giới siêu nhiên, rồi thế giới siêu nhiên... cũng sẽ nhìn lại cậu.</t>
+          <t>Nhìn lâu vào thế giới siêu nhiên, rồi thế giới siêu nhiên... cũng sẽ nhìn lại mày.</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>…Mayo. Ta biết là ngươi đấy, phải không?</t>
+          <t>…Mayo. Tao biết là mày đấy, phải không?</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ôi, ngươi phát hiện nhanh thế?! Ta còn chẳng thèm đổi cả avatar lẫn tên mà ngươi vẫn không bị lừa!</t>
+          <t>Ôi, mày phát hiện nhanh thế?! Tao còn chẳng thèm đổi cả avatar lẫn tên mà mày vẫn không bị lừa!</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>…Mayo. Ta biết là ngươi đấy, phải không?</t>
+          <t>…Mayo. Tao biết là mày đấy, phải không?</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Để ta nói thế này, nếu là một câu chuyện không giải thích được hay tin đồn siêu nhiên ở Lahai-Roi—dù là trực tiếp chứng kiến, nghe kể lại, hay chỉ là lời đồn—thì đều có trong hồ sơ của ta cả.</t>
+          <t>Để tao nói thế này, nếu là một câu chuyện không giải thích được hay tin đồn siêu nhiên ở Lahai-Roi—dù là trực tiếp chứng kiến, nghe kể lại, hay chỉ là lời đồn—thì đều có trong hồ sơ của tao cả.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Ta cũng không chắc lắm... nên mới hỏi ngươi có tin ta không chứ!</t>
+          <t>Tao cũng không chắc lắm... nên mới hỏi mày có tin tao không chứ!</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>…Được rồi. Ngươi nợ ta đấy.</t>
+          <t>…Được rồi. Mày nợ tao đấy.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Nửa đêm se lạnh, nhịp tim rộn ràng… Hử? Có phải ta vừa nghe thấy tiếng gió và tiếng kim loại cọ xát bên kia không?</t>
+          <t>Nửa đêm se lạnh, nhịp tim rộn ràng… Hử? Có phải tao vừa nghe thấy tiếng gió và tiếng kim loại cọ xát bên kia không?</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Ta đang ở hiện trường, gần đường ray.</t>
+          <t>Tao đang ở hiện trường, gần đường ray.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Không đâu! Huyền thoại đô thị này khác mà. Nó có thật đấy. Hoàn toàn chính xác... Ta đã tận mắt chứng kiến rồi.</t>
+          <t>Không đâu! Huyền thoại đô thị này khác mà. Nó có thật đấy. Hoàn toàn chính xác... Tao đã tận mắt chứng kiến rồi.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo cậu muốn ta phải đi điều tra vụ này.</t>
+          <t>Đừng có mà bảo cậu muốn tao phải đi điều tra vụ này.</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu thế nào rồi?... Cậu nghe thấy ta chứ?</t>
+          <t>{PlayerName}, cậu thế nào rồi?... Cậu nghe thấy tao chứ?</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Đợi đã, cái gì!? Này! Alo!? Tín hiệu của cậu... đang... đứt... Đừng làm gì liều lĩnh! Nghe ta nói đây—?!</t>
+          <t>Đợi đã, cái gì!? Này! Alo!? Tín hiệu của cậu... đang... đứt... Đừng làm gì liều lĩnh! Nghe tao nói đây—?!</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Ôi trời, chẳng thấy hồi âm gì cả... Nếu có chuyện gì xảy ra với {Male=hắn;Female=nàng}... Ta... ta lẽ ra phải gọi hỗ trợ ngay mới phải...</t>
+          <t>Ôi trời, chẳng thấy hồi âm gì cả... Nếu có chuyện gì xảy ra với {Male=him;Female=her}... Ta... ta lẽ ra phải gọi hỗ trợ ngay mới phải...</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Hừm, á! Ngươi... ngươi suýt làm ta sợ chết đi được!</t>
+          <t>Hừm, á! Mày... mày suýt làm tao sợ chết đi được!</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Ừ. Ta còn chụp tấm ảnh này cho cậu nữa cơ.</t>
+          <t>Ừ. Tao còn chụp tấm ảnh này cho cậu nữa cơ.</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Ta sẽ phải nâng cấp độ phân loại và ưu tiên điều tra. Chúng ta cần nghiên cứu sâu hơn và xác minh kỹ lưỡng để đưa ra kết luận.</t>
+          <t>Tao sẽ phải nâng cấp độ phân loại và ưu tiên điều tra. Chúng ta cần nghiên cứu sâu hơn và xác minh kỹ lưỡng để đưa ra kết luận.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Và cậu chính là người mà ta đang rất nỗ lực chiêu mộ đấy. Phải hoàn toàn trung thực mới được!</t>
+          <t>Và cậu chính là người mà tao đang rất nỗ lực chiêu mộ đấy. Phải hoàn toàn trung thực mới được!</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Pfft, ta sai à? Ta là chuyên gia về những chuyện siêu nhiên đấy. Chắc là ta có vài... tài lẻ thôi.</t>
+          <t>Pfft, tao sai à? Tao là chuyên gia về những chuyện siêu nhiên đấy. Chắc là tao có vài... tài lẻ thôi.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hắn không đồng ý. Nhưng cũng không từ chối. Hắn chỉ nói với ta rằng—</t>
+          <t>Hắn không đồng ý. Nhưng cũng không từ chối. Hắn chỉ nói với tao rằng—</t>
         </is>
       </c>
     </row>
